--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/54.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/54.xlsx
@@ -426,13 +426,13 @@
         <v>-7.461803674664226</v>
       </c>
       <c r="E2">
-        <v>-16.33999974063039</v>
+        <v>-30.95700814258877</v>
       </c>
       <c r="F2">
-        <v>-5.16884623886846</v>
+        <v>-5.728853252754829</v>
       </c>
       <c r="G2">
-        <v>-10.9513851109436</v>
+        <v>-19.31326531621925</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.613269038329593</v>
       </c>
       <c r="E3">
-        <v>-17.52727505596141</v>
+        <v>-31.17665724585681</v>
       </c>
       <c r="F3">
-        <v>-4.801712149212913</v>
+        <v>-5.707457351107921</v>
       </c>
       <c r="G3">
-        <v>-11.81433839557434</v>
+        <v>-19.96278441938764</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.720097454922429</v>
       </c>
       <c r="E4">
-        <v>-16.99838551965757</v>
+        <v>-30.42239687937624</v>
       </c>
       <c r="F4">
-        <v>-4.904365922870037</v>
+        <v>-5.789239579684108</v>
       </c>
       <c r="G4">
-        <v>-11.85686897411736</v>
+        <v>-19.73384364261934</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.769199136851806</v>
       </c>
       <c r="E5">
-        <v>-17.92604342012884</v>
+        <v>-32.03982514798486</v>
       </c>
       <c r="F5">
-        <v>-4.705831107441079</v>
+        <v>-5.788989412728462</v>
       </c>
       <c r="G5">
-        <v>-11.70060791411822</v>
+        <v>-19.61746969055011</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.760127294770732</v>
       </c>
       <c r="E6">
-        <v>-18.5770975997376</v>
+        <v>-31.80121532404669</v>
       </c>
       <c r="F6">
-        <v>-4.872973283406144</v>
+        <v>-5.645863264505361</v>
       </c>
       <c r="G6">
-        <v>-10.91825317118657</v>
+        <v>-19.55833176030934</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.692976410507161</v>
       </c>
       <c r="E7">
-        <v>-18.89444852972113</v>
+        <v>-32.2935419612126</v>
       </c>
       <c r="F7">
-        <v>-4.851994878930246</v>
+        <v>-5.583664469698757</v>
       </c>
       <c r="G7">
-        <v>-11.5228945190246</v>
+        <v>-19.69108794697965</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.570293140911032</v>
       </c>
       <c r="E8">
-        <v>-18.50953729601717</v>
+        <v>-32.97262060221783</v>
       </c>
       <c r="F8">
-        <v>-4.366405079041773</v>
+        <v>-5.43859248644648</v>
       </c>
       <c r="G8">
-        <v>-11.00369504100962</v>
+        <v>-18.82035819087716</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.396591255459357</v>
       </c>
       <c r="E9">
-        <v>-18.84722107429514</v>
+        <v>-33.45162673309017</v>
       </c>
       <c r="F9">
-        <v>-4.534285330362732</v>
+        <v>-5.47270382772636</v>
       </c>
       <c r="G9">
-        <v>-11.11976938870755</v>
+        <v>-18.91607764932688</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.178379192559549</v>
       </c>
       <c r="E10">
-        <v>-19.47487662870627</v>
+        <v>-34.34296853625693</v>
       </c>
       <c r="F10">
-        <v>-4.32896121570043</v>
+        <v>-5.379041153859223</v>
       </c>
       <c r="G10">
-        <v>-11.74487983961489</v>
+        <v>-19.153728471409</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.923818119256746</v>
       </c>
       <c r="E11">
-        <v>-20.15262163411623</v>
+        <v>-33.43941117445448</v>
       </c>
       <c r="F11">
-        <v>-3.97926923007823</v>
+        <v>-5.447745117880012</v>
       </c>
       <c r="G11">
-        <v>-10.70553075701516</v>
+        <v>-18.77546057227357</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.642670333677711</v>
       </c>
       <c r="E12">
-        <v>-20.47929669208156</v>
+        <v>-34.5255588724832</v>
       </c>
       <c r="F12">
-        <v>-3.807143595817923</v>
+        <v>-5.389608636816737</v>
       </c>
       <c r="G12">
-        <v>-10.7912076755715</v>
+        <v>-18.7974276971994</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.342736748558155</v>
       </c>
       <c r="E13">
-        <v>-20.27078763487238</v>
+        <v>-34.70678160955916</v>
       </c>
       <c r="F13">
-        <v>-4.105775843098965</v>
+        <v>-5.384174546654372</v>
       </c>
       <c r="G13">
-        <v>-10.07168377642968</v>
+        <v>-18.74145630376694</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.03724791756754</v>
       </c>
       <c r="E14">
-        <v>-22.38165428101578</v>
+        <v>-34.59647930391733</v>
       </c>
       <c r="F14">
-        <v>-3.454923432882379</v>
+        <v>-5.091446073853083</v>
       </c>
       <c r="G14">
-        <v>-10.699532048498</v>
+        <v>-18.04128088802939</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.735314062910134</v>
       </c>
       <c r="E15">
-        <v>-22.73546848370908</v>
+        <v>-35.9094175087242</v>
       </c>
       <c r="F15">
-        <v>-3.702927521239121</v>
+        <v>-5.04611366773488</v>
       </c>
       <c r="G15">
-        <v>-10.19739843273797</v>
+        <v>-17.75352330393764</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.447625893703247</v>
       </c>
       <c r="E16">
-        <v>-23.30506447286786</v>
+        <v>-35.77970163501148</v>
       </c>
       <c r="F16">
-        <v>-3.26419680859221</v>
+        <v>-4.897680169562042</v>
       </c>
       <c r="G16">
-        <v>-9.08228089438094</v>
+        <v>-17.78867302120085</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.183540801254156</v>
       </c>
       <c r="E17">
-        <v>-22.17217160189496</v>
+        <v>-36.15963834001802</v>
       </c>
       <c r="F17">
-        <v>-2.873707728382134</v>
+        <v>-4.753333007787214</v>
       </c>
       <c r="G17">
-        <v>-8.888776197064999</v>
+        <v>-17.4223495703711</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.952349751376587</v>
       </c>
       <c r="E18">
-        <v>-24.12104567583598</v>
+        <v>-36.61838860665405</v>
       </c>
       <c r="F18">
-        <v>-2.866594537494295</v>
+        <v>-4.579576318110796</v>
       </c>
       <c r="G18">
-        <v>-8.697075747067963</v>
+        <v>-16.92487885800313</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.763255975088132</v>
       </c>
       <c r="E19">
-        <v>-23.3784121663701</v>
+        <v>-37.41826882028789</v>
       </c>
       <c r="F19">
-        <v>-2.867316045502133</v>
+        <v>-4.456273830204089</v>
       </c>
       <c r="G19">
-        <v>-8.450817506583736</v>
+        <v>-16.76668609468183</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.623293405396902</v>
       </c>
       <c r="E20">
-        <v>-25.01232181612962</v>
+        <v>-37.9924227185354</v>
       </c>
       <c r="F20">
-        <v>-2.306061510307148</v>
+        <v>-4.317912451281891</v>
       </c>
       <c r="G20">
-        <v>-8.482992698679913</v>
+        <v>-16.75535078675536</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.541850126946439</v>
       </c>
       <c r="E21">
-        <v>-25.82559046316715</v>
+        <v>-38.52631621861772</v>
       </c>
       <c r="F21">
-        <v>-2.165526495320004</v>
+        <v>-4.422507089763773</v>
       </c>
       <c r="G21">
-        <v>-9.112598870429586</v>
+        <v>-16.62784843585587</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.522199672634573</v>
       </c>
       <c r="E22">
-        <v>-25.36143546280296</v>
+        <v>-38.81886469646123</v>
       </c>
       <c r="F22">
-        <v>-2.49250133328783</v>
+        <v>-4.111758312481983</v>
       </c>
       <c r="G22">
-        <v>-8.87683174875931</v>
+        <v>-16.80076981628139</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.568746063476893</v>
       </c>
       <c r="E23">
-        <v>-25.50855199789014</v>
+        <v>-39.19744512350248</v>
       </c>
       <c r="F23">
-        <v>-2.052661436688571</v>
+        <v>-4.106555336824999</v>
       </c>
       <c r="G23">
-        <v>-8.747498666176602</v>
+        <v>-16.47997464298048</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.681234832607592</v>
       </c>
       <c r="E24">
-        <v>-25.69968530033189</v>
+        <v>-39.07520123190242</v>
       </c>
       <c r="F24">
-        <v>-2.258808948549256</v>
+        <v>-3.760628281048523</v>
       </c>
       <c r="G24">
-        <v>-8.894129349202002</v>
+        <v>-16.65385773688515</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.856575763670303</v>
       </c>
       <c r="E25">
-        <v>-26.07058090698211</v>
+        <v>-39.66405455677882</v>
       </c>
       <c r="F25">
-        <v>-2.246758687940731</v>
+        <v>-3.788799399682929</v>
       </c>
       <c r="G25">
-        <v>-8.360062211170156</v>
+        <v>-16.52654739762694</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.08914969614344</v>
       </c>
       <c r="E26">
-        <v>-24.6302091793624</v>
+        <v>-39.70415419411674</v>
       </c>
       <c r="F26">
-        <v>-2.038593273086827</v>
+        <v>-3.760509824509922</v>
       </c>
       <c r="G26">
-        <v>-8.23826393023483</v>
+        <v>-16.14334181981969</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.369464052405895</v>
       </c>
       <c r="E27">
-        <v>-25.88527575058824</v>
+        <v>-38.86044967327367</v>
       </c>
       <c r="F27">
-        <v>-1.83314656004891</v>
+        <v>-3.867124851087233</v>
       </c>
       <c r="G27">
-        <v>-8.253552029535184</v>
+        <v>-16.78957520654035</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.687597611207502</v>
       </c>
       <c r="E28">
-        <v>-26.2083687856135</v>
+        <v>-39.70375342416706</v>
       </c>
       <c r="F28">
-        <v>-1.769572675353659</v>
+        <v>-3.983855072020128</v>
       </c>
       <c r="G28">
-        <v>-8.512946514719239</v>
+        <v>-17.15725432576842</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.027915068245422</v>
       </c>
       <c r="E29">
-        <v>-25.51170381579948</v>
+        <v>-39.35006375450898</v>
       </c>
       <c r="F29">
-        <v>-2.119050942185937</v>
+        <v>-4.064631662569316</v>
       </c>
       <c r="G29">
-        <v>-8.829490947547731</v>
+        <v>-16.39400805168945</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.378232729669163</v>
       </c>
       <c r="E30">
-        <v>-25.32604543843301</v>
+        <v>-39.40182647665366</v>
       </c>
       <c r="F30">
-        <v>-2.158845712216425</v>
+        <v>-3.813724146465763</v>
       </c>
       <c r="G30">
-        <v>-9.129466099952172</v>
+        <v>-16.6603315086872</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.724395184327234</v>
       </c>
       <c r="E31">
-        <v>-24.28575986091697</v>
+        <v>-39.9630108253432</v>
       </c>
       <c r="F31">
-        <v>-2.229316583907385</v>
+        <v>-3.834311561527539</v>
       </c>
       <c r="G31">
-        <v>-9.263953701939524</v>
+        <v>-17.09607544420269</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.052920445576175</v>
       </c>
       <c r="E32">
-        <v>-25.10607028503642</v>
+        <v>-39.29487977025151</v>
       </c>
       <c r="F32">
-        <v>-2.156105472847964</v>
+        <v>-3.983524553426411</v>
       </c>
       <c r="G32">
-        <v>-9.189062540750133</v>
+        <v>-17.25599300174996</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.351901098883711</v>
       </c>
       <c r="E33">
-        <v>-24.61311871845745</v>
+        <v>-38.59141982518899</v>
       </c>
       <c r="F33">
-        <v>-2.152060554820094</v>
+        <v>-3.941486564469142</v>
       </c>
       <c r="G33">
-        <v>-9.676510576497961</v>
+        <v>-17.03210908329289</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.610969036583243</v>
       </c>
       <c r="E34">
-        <v>-23.68518910954572</v>
+        <v>-37.51210106596383</v>
       </c>
       <c r="F34">
-        <v>-2.268652438396722</v>
+        <v>-3.859354764848974</v>
       </c>
       <c r="G34">
-        <v>-9.653767128643167</v>
+        <v>-17.50527873612985</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.822802955132609</v>
       </c>
       <c r="E35">
-        <v>-22.98841545635552</v>
+        <v>-38.37437459447536</v>
       </c>
       <c r="F35">
-        <v>-2.504268292244597</v>
+        <v>-3.876278310888167</v>
       </c>
       <c r="G35">
-        <v>-9.405635119383714</v>
+        <v>-17.52871574327512</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.982043036835859</v>
       </c>
       <c r="E36">
-        <v>-23.33128433737227</v>
+        <v>-38.27054800666449</v>
       </c>
       <c r="F36">
-        <v>-2.263362484162445</v>
+        <v>-4.171051194439566</v>
       </c>
       <c r="G36">
-        <v>-9.287806182549973</v>
+        <v>-17.35046438453137</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.088060082610118</v>
       </c>
       <c r="E37">
-        <v>-24.11590585783727</v>
+        <v>-37.41825976333988</v>
       </c>
       <c r="F37">
-        <v>-2.222578643453013</v>
+        <v>-3.69393807818394</v>
       </c>
       <c r="G37">
-        <v>-9.047126211299419</v>
+        <v>-17.22931662579451</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.143512919201219</v>
       </c>
       <c r="E38">
-        <v>-22.40283848242366</v>
+        <v>-37.01544973612059</v>
       </c>
       <c r="F38">
-        <v>-1.948625117836175</v>
+        <v>-4.111521399404782</v>
       </c>
       <c r="G38">
-        <v>-9.426577630465143</v>
+        <v>-17.3688610860931</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.152647415563923</v>
       </c>
       <c r="E39">
-        <v>-22.31252259681469</v>
+        <v>-37.25064961913098</v>
       </c>
       <c r="F39">
-        <v>-2.388737547310955</v>
+        <v>-4.070137820695725</v>
       </c>
       <c r="G39">
-        <v>-9.496363930432981</v>
+        <v>-17.03789591689554</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.122156641945788</v>
       </c>
       <c r="E40">
-        <v>-22.65945804749033</v>
+        <v>-35.72964161909369</v>
       </c>
       <c r="F40">
-        <v>-2.253829632091028</v>
+        <v>-4.057098489408258</v>
       </c>
       <c r="G40">
-        <v>-9.955708745097937</v>
+        <v>-16.87723845242025</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.060510176082518</v>
       </c>
       <c r="E41">
-        <v>-21.90136885623627</v>
+        <v>-36.27118144753795</v>
       </c>
       <c r="F41">
-        <v>-2.152935310797451</v>
+        <v>-3.689501342374546</v>
       </c>
       <c r="G41">
-        <v>-9.45112532563884</v>
+        <v>-17.4349097801471</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.976695794385408</v>
       </c>
       <c r="E42">
-        <v>-21.45212612077934</v>
+        <v>-35.92964393787945</v>
       </c>
       <c r="F42">
-        <v>-2.293329503326119</v>
+        <v>-4.011653425323274</v>
       </c>
       <c r="G42">
-        <v>-9.767090412997961</v>
+        <v>-17.30265348585321</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.882572714098779</v>
       </c>
       <c r="E43">
-        <v>-20.66881332930256</v>
+        <v>-35.19557377276208</v>
       </c>
       <c r="F43">
-        <v>-2.398285309995623</v>
+        <v>-3.797041655340784</v>
       </c>
       <c r="G43">
-        <v>-9.343727917799344</v>
+        <v>-17.38597660653113</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.788504648558522</v>
       </c>
       <c r="E44">
-        <v>-20.09492887525851</v>
+        <v>-35.06236418135245</v>
       </c>
       <c r="F44">
-        <v>-2.59859863023839</v>
+        <v>-4.063355148401603</v>
       </c>
       <c r="G44">
-        <v>-9.924814734125457</v>
+        <v>-16.53095869955802</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.706984420446992</v>
       </c>
       <c r="E45">
-        <v>-20.92451814261968</v>
+        <v>-35.24481187064748</v>
       </c>
       <c r="F45">
-        <v>-2.25687222556151</v>
+        <v>-4.382172224186659</v>
       </c>
       <c r="G45">
-        <v>-8.580034720072568</v>
+        <v>-17.2575936505182</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.647898913399199</v>
       </c>
       <c r="E46">
-        <v>-20.00667797379704</v>
+        <v>-34.78311583166946</v>
       </c>
       <c r="F46">
-        <v>-2.346956352248554</v>
+        <v>-4.013219039714565</v>
       </c>
       <c r="G46">
-        <v>-8.912641919857606</v>
+        <v>-17.0373314688811</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.620014873718806</v>
       </c>
       <c r="E47">
-        <v>-19.89484730817761</v>
+        <v>-34.32191339635827</v>
       </c>
       <c r="F47">
-        <v>-2.572732858085976</v>
+        <v>-4.033512384348347</v>
       </c>
       <c r="G47">
-        <v>-9.129509137044183</v>
+        <v>-17.11584933270876</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.630505223246686</v>
       </c>
       <c r="E48">
-        <v>-18.76390620950202</v>
+        <v>-34.51412900408784</v>
       </c>
       <c r="F48">
-        <v>-2.345151339677854</v>
+        <v>-4.417500437181253</v>
       </c>
       <c r="G48">
-        <v>-9.144853515618705</v>
+        <v>-16.91248583077687</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.68210771028411</v>
       </c>
       <c r="E49">
-        <v>-18.77595195036242</v>
+        <v>-34.3754241094699</v>
       </c>
       <c r="F49">
-        <v>-2.9121348638306</v>
+        <v>-4.198432050571701</v>
       </c>
       <c r="G49">
-        <v>-9.56241262448698</v>
+        <v>-17.21405997667678</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.779856940905137</v>
       </c>
       <c r="E50">
-        <v>-18.70467376948169</v>
+        <v>-33.75637718414736</v>
       </c>
       <c r="F50">
-        <v>-3.006480112437645</v>
+        <v>-4.157037703086407</v>
       </c>
       <c r="G50">
-        <v>-8.805820546941943</v>
+        <v>-17.27043360139226</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.921628535057697</v>
       </c>
       <c r="E51">
-        <v>-18.94727317902061</v>
+        <v>-32.88212131341154</v>
       </c>
       <c r="F51">
-        <v>-3.02319408152393</v>
+        <v>-3.983222199324389</v>
       </c>
       <c r="G51">
-        <v>-9.53565348489305</v>
+        <v>-17.01126919912318</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.107640652127074</v>
       </c>
       <c r="E52">
-        <v>-19.02792530109722</v>
+        <v>-33.1897450812266</v>
       </c>
       <c r="F52">
-        <v>-2.87015568895893</v>
+        <v>-4.431641497114443</v>
       </c>
       <c r="G52">
-        <v>-8.860484274886389</v>
+        <v>-17.2175476364024</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.332873274579539</v>
       </c>
       <c r="E53">
-        <v>-18.78813354544306</v>
+        <v>-32.97013446998762</v>
       </c>
       <c r="F53">
-        <v>-2.940412013492565</v>
+        <v>-3.984201329594498</v>
       </c>
       <c r="G53">
-        <v>-9.208869534711592</v>
+        <v>-17.06852177367934</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.589786561849095</v>
       </c>
       <c r="E54">
-        <v>-18.88027440607712</v>
+        <v>-32.17852551412879</v>
       </c>
       <c r="F54">
-        <v>-3.268213562128385</v>
+        <v>-4.284016485526737</v>
       </c>
       <c r="G54">
-        <v>-9.770573106905273</v>
+        <v>-16.72036328622357</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.868380844657571</v>
       </c>
       <c r="E55">
-        <v>-17.61560746995502</v>
+        <v>-32.67218352265294</v>
       </c>
       <c r="F55">
-        <v>-3.315322816325593</v>
+        <v>-4.326520845331783</v>
       </c>
       <c r="G55">
-        <v>-10.40324484382431</v>
+        <v>-17.52301332858372</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.15556843594945</v>
       </c>
       <c r="E56">
-        <v>-17.78011787370567</v>
+        <v>-32.11741828586928</v>
       </c>
       <c r="F56">
-        <v>-3.118869688179871</v>
+        <v>-4.289669264683441</v>
       </c>
       <c r="G56">
-        <v>-9.055177458050927</v>
+        <v>-16.74957388478933</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.441388306604255</v>
       </c>
       <c r="E57">
-        <v>-17.8844539148424</v>
+        <v>-31.86719292610145</v>
       </c>
       <c r="F57">
-        <v>-2.946181592453063</v>
+        <v>-4.359001131195551</v>
       </c>
       <c r="G57">
-        <v>-9.58852951824629</v>
+        <v>-16.99220376736252</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.710675368049698</v>
       </c>
       <c r="E58">
-        <v>-18.02200178435138</v>
+        <v>-31.76446222900044</v>
       </c>
       <c r="F58">
-        <v>-3.213837040706417</v>
+        <v>-4.342380767625782</v>
       </c>
       <c r="G58">
-        <v>-9.057868931574355</v>
+        <v>-17.29664650097221</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.955984287919939</v>
       </c>
       <c r="E59">
-        <v>-17.8554082825572</v>
+        <v>-31.58764343289695</v>
       </c>
       <c r="F59">
-        <v>-3.325884500711286</v>
+        <v>-4.517630175362045</v>
       </c>
       <c r="G59">
-        <v>-9.224806500937643</v>
+        <v>-17.16735811075428</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.16826568973375</v>
       </c>
       <c r="E60">
-        <v>-17.8222870236651</v>
+        <v>-31.71798197178571</v>
       </c>
       <c r="F60">
-        <v>-3.667900833979146</v>
+        <v>-4.387079472680844</v>
       </c>
       <c r="G60">
-        <v>-9.88819347937004</v>
+        <v>-17.7810438690056</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.34041011736087</v>
       </c>
       <c r="E61">
-        <v>-17.45515457891525</v>
+        <v>-31.29417341059287</v>
       </c>
       <c r="F61">
-        <v>-3.487693647337128</v>
+        <v>-4.301900109385776</v>
       </c>
       <c r="G61">
-        <v>-10.43157649254939</v>
+        <v>-17.62317719441991</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.46782517876626</v>
       </c>
       <c r="E62">
-        <v>-17.18553376497256</v>
+        <v>-31.33799318932808</v>
       </c>
       <c r="F62">
-        <v>-3.558267236586035</v>
+        <v>-4.44989457283513</v>
       </c>
       <c r="G62">
-        <v>-9.764723372937381</v>
+        <v>-17.98648804880892</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.54683341638461</v>
       </c>
       <c r="E63">
-        <v>-17.40502890012435</v>
+        <v>-30.5991318987106</v>
       </c>
       <c r="F63">
-        <v>-3.610533077865669</v>
+        <v>-4.504425998961421</v>
       </c>
       <c r="G63">
-        <v>-9.896509569764689</v>
+        <v>-17.41946774047917</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.57830385691942</v>
       </c>
       <c r="E64">
-        <v>-17.90830085896679</v>
+        <v>-31.29201559272821</v>
       </c>
       <c r="F64">
-        <v>-3.390621413240068</v>
+        <v>-4.517363441058344</v>
       </c>
       <c r="G64">
-        <v>-9.560439539345573</v>
+        <v>-17.47955910783525</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.56257386921654</v>
       </c>
       <c r="E65">
-        <v>-17.81617358375474</v>
+        <v>-31.11504735698246</v>
       </c>
       <c r="F65">
-        <v>-3.683037591530502</v>
+        <v>-4.557809307867433</v>
       </c>
       <c r="G65">
-        <v>-9.621843538007976</v>
+        <v>-18.15911479068145</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.50559789961419</v>
       </c>
       <c r="E66">
-        <v>-16.68333505446994</v>
+        <v>-30.29141303294138</v>
       </c>
       <c r="F66">
-        <v>-3.365898788103517</v>
+        <v>-4.663348285188507</v>
       </c>
       <c r="G66">
-        <v>-9.734342496523489</v>
+        <v>-18.16244685476672</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.41334259244681</v>
       </c>
       <c r="E67">
-        <v>-17.68129751391029</v>
+        <v>-31.38161145096997</v>
       </c>
       <c r="F67">
-        <v>-3.415091386318765</v>
+        <v>-4.876484732826611</v>
       </c>
       <c r="G67">
-        <v>-10.38618891320599</v>
+        <v>-17.69250498383056</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.29220476886927</v>
       </c>
       <c r="E68">
-        <v>-16.60448979352239</v>
+        <v>-30.91969351676557</v>
       </c>
       <c r="F68">
-        <v>-3.636714457998551</v>
+        <v>-4.684622416827203</v>
       </c>
       <c r="G68">
-        <v>-10.03075219138213</v>
+        <v>-17.77258211460722</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.14938146882573</v>
       </c>
       <c r="E69">
-        <v>-17.37958340467524</v>
+        <v>-30.47600269044204</v>
       </c>
       <c r="F69">
-        <v>-3.970384161315803</v>
+        <v>-4.666964937269129</v>
       </c>
       <c r="G69">
-        <v>-9.843749405505324</v>
+        <v>-18.38671479650634</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.991006245873326</v>
       </c>
       <c r="E70">
-        <v>-17.29481037125166</v>
+        <v>-30.92872782241087</v>
       </c>
       <c r="F70">
-        <v>-3.366713073260469</v>
+        <v>-4.75551244242398</v>
       </c>
       <c r="G70">
-        <v>-9.506805391063841</v>
+        <v>-17.59884965052458</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.823457200198622</v>
       </c>
       <c r="E71">
-        <v>-17.30102343759018</v>
+        <v>-30.81318833657917</v>
       </c>
       <c r="F71">
-        <v>-3.542408142659438</v>
+        <v>-4.902559253564531</v>
       </c>
       <c r="G71">
-        <v>-9.432973604447016</v>
+        <v>-17.69092088779002</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.654330730150578</v>
       </c>
       <c r="E72">
-        <v>-16.96491103979287</v>
+        <v>-30.85609109932784</v>
       </c>
       <c r="F72">
-        <v>-3.629294771171675</v>
+        <v>-5.138517223149762</v>
       </c>
       <c r="G72">
-        <v>-10.3813257218088</v>
+        <v>-17.61200741377041</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.489937894893201</v>
       </c>
       <c r="E73">
-        <v>-17.92188175251579</v>
+        <v>-30.85737945018302</v>
       </c>
       <c r="F73">
-        <v>-3.680701595454607</v>
+        <v>-4.911684548873771</v>
       </c>
       <c r="G73">
-        <v>-8.9676300812649</v>
+        <v>-17.79644287158152</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.336392582948609</v>
       </c>
       <c r="E74">
-        <v>-17.72710755697188</v>
+        <v>-31.39831472734726</v>
       </c>
       <c r="F74">
-        <v>-3.59764699454772</v>
+        <v>-4.935436327414241</v>
       </c>
       <c r="G74">
-        <v>-9.076119969132357</v>
+        <v>-17.52225024783692</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.197121099081514</v>
       </c>
       <c r="E75">
-        <v>-19.09474293508039</v>
+        <v>-31.04541301216651</v>
       </c>
       <c r="F75">
-        <v>-3.662882584252987</v>
+        <v>-5.202080339068776</v>
       </c>
       <c r="G75">
-        <v>-9.792498850011865</v>
+        <v>-17.50946161041871</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.073980512761043</v>
       </c>
       <c r="E76">
-        <v>-19.47344110244583</v>
+        <v>-31.05002299870632</v>
       </c>
       <c r="F76">
-        <v>-4.224894247254131</v>
+        <v>-5.358008905502144</v>
       </c>
       <c r="G76">
-        <v>-8.180736580398914</v>
+        <v>-17.59549110207499</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.966812568815097</v>
       </c>
       <c r="E77">
-        <v>-19.19935974160559</v>
+        <v>-32.11384531987723</v>
       </c>
       <c r="F77">
-        <v>-3.99923951142492</v>
+        <v>-5.556878381361832</v>
       </c>
       <c r="G77">
-        <v>-8.058832362006331</v>
+        <v>-17.40651192051123</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.87162330513527</v>
       </c>
       <c r="E78">
-        <v>-19.20694040709443</v>
+        <v>-31.65766949071456</v>
       </c>
       <c r="F78">
-        <v>-4.256254580389315</v>
+        <v>-5.178873626279348</v>
       </c>
       <c r="G78">
-        <v>-9.468926129003501</v>
+        <v>-17.24263329522623</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.788880895207971</v>
       </c>
       <c r="E79">
-        <v>-19.11315118192157</v>
+        <v>-31.79473734197872</v>
       </c>
       <c r="F79">
-        <v>-4.170269215611324</v>
+        <v>-5.529520719516976</v>
       </c>
       <c r="G79">
-        <v>-8.841584370402689</v>
+        <v>-17.20639109793506</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.713837918557259</v>
       </c>
       <c r="E80">
-        <v>-19.21483806576381</v>
+        <v>-32.32112263215632</v>
       </c>
       <c r="F80">
-        <v>-3.996107454274936</v>
+        <v>-5.135984903999404</v>
       </c>
       <c r="G80">
-        <v>-9.129850123234728</v>
+        <v>-16.93889405254363</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.644341141935593</v>
       </c>
       <c r="E81">
-        <v>-19.46961001343535</v>
+        <v>-32.79022046189988</v>
       </c>
       <c r="F81">
-        <v>-4.435712922899202</v>
+        <v>-5.348978044076824</v>
       </c>
       <c r="G81">
-        <v>-8.730843311568529</v>
+        <v>-16.5276945016563</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.576660483900126</v>
       </c>
       <c r="E82">
-        <v>-20.42753623417389</v>
+        <v>-33.16811708936596</v>
       </c>
       <c r="F82">
-        <v>-3.972154382455585</v>
+        <v>-5.233634510176215</v>
       </c>
       <c r="G82">
-        <v>-9.187347678160791</v>
+        <v>-17.07490119493351</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.508032192280565</v>
       </c>
       <c r="E83">
-        <v>-21.25067695454813</v>
+        <v>-33.80703495863416</v>
       </c>
       <c r="F83">
-        <v>-4.350884787382922</v>
+        <v>-5.383915267657295</v>
       </c>
       <c r="G83">
-        <v>-8.560734239578618</v>
+        <v>-16.8059590964142</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.436523047989075</v>
       </c>
       <c r="E84">
-        <v>-21.75392174254653</v>
+        <v>-34.13770413067425</v>
       </c>
       <c r="F84">
-        <v>-4.097003432303318</v>
+        <v>-5.537416717600461</v>
       </c>
       <c r="G84">
-        <v>-8.611418691784859</v>
+        <v>-16.72925375626929</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.358542037335384</v>
       </c>
       <c r="E85">
-        <v>-22.04571396523077</v>
+        <v>-35.32849354183522</v>
       </c>
       <c r="F85">
-        <v>-4.428733099163214</v>
+        <v>-5.314378794396694</v>
       </c>
       <c r="G85">
-        <v>-8.72234183062368</v>
+        <v>-16.92001070078763</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.2769912459453</v>
       </c>
       <c r="E86">
-        <v>-23.79104218947501</v>
+        <v>-35.47913775817438</v>
       </c>
       <c r="F86">
-        <v>-4.499616497820767</v>
+        <v>-5.647568044620322</v>
       </c>
       <c r="G86">
-        <v>-8.094437279281193</v>
+        <v>-16.4975701925217</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.190994291596491</v>
       </c>
       <c r="E87">
-        <v>-24.31163103292279</v>
+        <v>-36.07571213123386</v>
       </c>
       <c r="F87">
-        <v>-4.36058662640451</v>
+        <v>-5.777328484799254</v>
       </c>
       <c r="G87">
-        <v>-8.749624036412815</v>
+        <v>-16.93845209471414</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.103984376997253</v>
       </c>
       <c r="E88">
-        <v>-25.88036235628992</v>
+        <v>-36.71997359983112</v>
       </c>
       <c r="F88">
-        <v>-4.426425267579014</v>
+        <v>-5.467338492058428</v>
       </c>
       <c r="G88">
-        <v>-8.692762106230292</v>
+        <v>-16.62792623367605</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.017713916045306</v>
       </c>
       <c r="E89">
-        <v>-26.07314402327045</v>
+        <v>-37.97413674049243</v>
       </c>
       <c r="F89">
-        <v>-4.709613433002262</v>
+        <v>-5.629961923841222</v>
       </c>
       <c r="G89">
-        <v>-8.925433867821349</v>
+        <v>-17.32025069066721</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.933903434667663</v>
       </c>
       <c r="E90">
-        <v>-27.47447577647004</v>
+        <v>-38.83665933507437</v>
       </c>
       <c r="F90">
-        <v>-4.642444433778861</v>
+        <v>-5.465125094358148</v>
       </c>
       <c r="G90">
-        <v>-9.080718316886404</v>
+        <v>-17.38679762182487</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.854046904595262</v>
       </c>
       <c r="E91">
-        <v>-29.38816360737145</v>
+        <v>-39.269785231538</v>
       </c>
       <c r="F91">
-        <v>-4.51803690375682</v>
+        <v>-5.662739593602596</v>
       </c>
       <c r="G91">
-        <v>-8.349329422531838</v>
+        <v>-16.49627080339754</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.777493018370846</v>
       </c>
       <c r="E92">
-        <v>-29.41097353094809</v>
+        <v>-40.02787668702906</v>
       </c>
       <c r="F92">
-        <v>-5.193572177474622</v>
+        <v>-5.767528898424136</v>
       </c>
       <c r="G92">
-        <v>-8.705140236001627</v>
+        <v>-17.3563339817725</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.707254154088291</v>
       </c>
       <c r="E93">
-        <v>-31.01353029091551</v>
+        <v>-41.7339407773898</v>
       </c>
       <c r="F93">
-        <v>-4.831125818951518</v>
+        <v>-5.802061878712041</v>
       </c>
       <c r="G93">
-        <v>-10.02458795558801</v>
+        <v>-17.02243566922714</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.642215835676211</v>
       </c>
       <c r="E94">
-        <v>-32.16399816951218</v>
+        <v>-43.20538689365015</v>
       </c>
       <c r="F94">
-        <v>-4.747620586177509</v>
+        <v>-5.837414942728719</v>
       </c>
       <c r="G94">
-        <v>-9.63331788884709</v>
+        <v>-16.66918059691367</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.586083432564923</v>
       </c>
       <c r="E95">
-        <v>-34.73921227616509</v>
+        <v>-44.11341612353517</v>
       </c>
       <c r="F95">
-        <v>-5.24223462055208</v>
+        <v>-6.096850501244093</v>
       </c>
       <c r="G95">
-        <v>-9.079092839026622</v>
+        <v>-16.81758573234812</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.540805074739362</v>
       </c>
       <c r="E96">
-        <v>-35.92945827044514</v>
+        <v>-46.20428955693471</v>
       </c>
       <c r="F96">
-        <v>-5.101405535136941</v>
+        <v>-6.141536780788113</v>
       </c>
       <c r="G96">
-        <v>-9.218132441130473</v>
+        <v>-16.69119241420429</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.507819031804478</v>
       </c>
       <c r="E97">
-        <v>-38.32590180869725</v>
+        <v>-46.99573095925526</v>
       </c>
       <c r="F97">
-        <v>-5.646244313510649</v>
+        <v>-5.838925884871425</v>
       </c>
       <c r="G97">
-        <v>-9.44585493714032</v>
+        <v>-17.7732756738977</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.490025733895364</v>
       </c>
       <c r="E98">
-        <v>-39.63458551217391</v>
+        <v>-48.91622961506421</v>
       </c>
       <c r="F98">
-        <v>-5.447813872374444</v>
+        <v>-5.85758651735429</v>
       </c>
       <c r="G98">
-        <v>-9.890726046707583</v>
+        <v>-17.17448074948202</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.486873133021795</v>
       </c>
       <c r="E99">
-        <v>-40.91751804820594</v>
+        <v>-50.66871735671459</v>
       </c>
       <c r="F99">
-        <v>-5.374157099652318</v>
+        <v>-5.946172127409668</v>
       </c>
       <c r="G99">
-        <v>-10.20693611443661</v>
+        <v>-17.72491687993279</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.502293373244695</v>
       </c>
       <c r="E100">
-        <v>-43.5970161185445</v>
+        <v>-51.15293802540676</v>
       </c>
       <c r="F100">
-        <v>-5.645584104690617</v>
+        <v>-6.264903052984835</v>
       </c>
       <c r="G100">
-        <v>-10.80795572545467</v>
+        <v>-18.07562448745379</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.532825125409139</v>
       </c>
       <c r="E101">
-        <v>-45.8067167099053</v>
+        <v>-52.79349094653554</v>
       </c>
       <c r="F101">
-        <v>-5.890007989132459</v>
+        <v>-6.443682962591829</v>
       </c>
       <c r="G101">
-        <v>-10.33857333671465</v>
+        <v>-18.07909228390618</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.584574391927974</v>
       </c>
       <c r="E102">
-        <v>-48.63641407401176</v>
+        <v>-55.57516950438317</v>
       </c>
       <c r="F102">
-        <v>-6.135279293427365</v>
+        <v>-6.189765159346503</v>
       </c>
       <c r="G102">
-        <v>-11.26332126438143</v>
+        <v>-17.95468529308591</v>
       </c>
     </row>
   </sheetData>
